--- a/doc/ProductBacklog_group066.xlsx
+++ b/doc/ProductBacklog_group066.xlsx
@@ -1690,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>14</v>
@@ -1722,7 +1722,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>21</v>
@@ -1754,7 +1754,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>28</v>
@@ -1783,7 +1783,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>21</v>
@@ -1815,7 +1815,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>21</v>
@@ -1879,7 +1879,7 @@
         <v>49</v>
       </c>
       <c r="G8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>44</v>
@@ -1937,7 +1937,7 @@
         <v>59</v>
       </c>
       <c r="G10" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>60</v>
@@ -1969,7 +1969,7 @@
         <v>66</v>
       </c>
       <c r="G11" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>60</v>
@@ -2001,7 +2001,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>60</v>
@@ -2033,7 +2033,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>15</v>
@@ -2062,7 +2062,7 @@
         <v>80</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>21</v>
@@ -2126,7 +2126,7 @@
         <v>88</v>
       </c>
       <c r="G16" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>22</v>
@@ -2184,7 +2184,7 @@
         <v>96</v>
       </c>
       <c r="G18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>22</v>
@@ -2213,7 +2213,7 @@
         <v>100</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>21</v>
@@ -2306,7 +2306,7 @@
         <v>112</v>
       </c>
       <c r="G22" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>60</v>
@@ -2338,7 +2338,7 @@
         <v>116</v>
       </c>
       <c r="G23" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>60</v>
@@ -2370,7 +2370,7 @@
         <v>120</v>
       </c>
       <c r="G24" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>60</v>
@@ -2402,7 +2402,7 @@
         <v>124</v>
       </c>
       <c r="G25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>125</v>
@@ -2434,7 +2434,7 @@
         <v>130</v>
       </c>
       <c r="G26" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>126</v>
@@ -2463,7 +2463,7 @@
         <v>135</v>
       </c>
       <c r="G27" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>126</v>
@@ -2553,7 +2553,7 @@
         <v>151</v>
       </c>
       <c r="G30" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>21</v>
@@ -2585,7 +2585,7 @@
         <v>155</v>
       </c>
       <c r="G31" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>60</v>
